--- a/experiments/results/cabp/cplex-cp-cabp.xlsx
+++ b/experiments/results/cabp/cplex-cp-cabp.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>30.34</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>196.7</t>
+          <t>208.3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>215.7</t>
+          <t>218.2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>215.1</t>
+          <t>218.9</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>27.95</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>160.2</t>
+          <t>160.8</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1800.08</t>
+          <t>1800.06</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>203.4</t>
+          <t>205.5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1800.00</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>170.7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1800.08</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1691,17 +1691,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>284</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>235.0</t>
+          <t>236.5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1800.12</t>
+          <t>1800.06</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>132.2</t>
+          <t>132.1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>42.28</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1816,12 +1816,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>216.2</t>
+          <t>217.6</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1800.09</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>229.6</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1800.09</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>304.8</t>
+          <t>309.1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>277.17</t>
+          <t>254.77</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>152.9</t>
+          <t>167.5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>251.5</t>
+          <t>254.4</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1800.06</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -2860,12 +2860,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>251.9</t>
+          <t>254.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.06</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>88.40</t>
+          <t>84.06</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2980,12 +2980,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>185.2</t>
+          <t>186.8</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1800.09</t>
+          <t>1800.03</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>229.2</t>
+          <t>230.3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.03</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -3158,12 +3158,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>194.5</t>
+          <t>196.8</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1800.05</t>
+          <t>1800.09</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -3211,17 +3211,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>424</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>281.8</t>
+          <t>282.8</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1800.07</t>
+          <t>1800.06</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>180.66</t>
+          <t>172.30</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>238.3</t>
+          <t>242.5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1800.07</t>
+          <t>1800.11</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -3394,12 +3394,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>388.6</t>
+          <t>392.9</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1800.13</t>
+          <t>1800.10</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -3452,12 +3452,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>354.5</t>
+          <t>366.7</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.08</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -3576,22 +3576,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>19.40</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -3896,12 +3896,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4020,15 +4020,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>281.9</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>1566.61</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4078,12 +4082,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -4140,7 +4144,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4202,12 +4206,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>28.40</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -4264,12 +4268,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -4316,7 +4320,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4326,12 +4330,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>235.9</t>
+          <t>237.5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1800.08</t>
+          <t>1800.06</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -4374,7 +4378,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -4384,12 +4388,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>236.2</t>
+          <t>237.7</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1800.00</t>
+          <t>1800.03</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -4442,12 +4446,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>102.6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>60.93</t>
+          <t>96.72</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -4494,22 +4498,22 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>192</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>434</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>214.2</t>
+          <t>212.9</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -4562,12 +4566,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -4614,7 +4618,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4624,12 +4628,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>232.8</t>
+          <t>238.7</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1800.06</t>
+          <t>1800.05</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -4672,12 +4676,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>517</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>517</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4687,7 +4691,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -4734,22 +4738,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>453</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>453</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>192.4</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>262.59</t>
+          <t>406.61</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -4806,12 +4810,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>119.7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>179.90</t>
+          <t>122.68</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -4858,22 +4862,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>657</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>657</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -4930,12 +4934,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>264.1</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1800.01</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -4988,12 +4992,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>311.1</t>
+          <t>315.4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1800.06</t>
+          <t>1800.09</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -5112,22 +5116,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -5184,12 +5188,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>31.31</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -5246,7 +5250,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -5308,12 +5312,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -5370,12 +5374,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -5432,12 +5436,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -5494,12 +5498,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -5556,12 +5560,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>297.5</t>
+          <t>301.2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -5614,12 +5618,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -5676,12 +5680,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -5738,12 +5742,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>52.79</t>
+          <t>45.47</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -5800,12 +5804,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -5852,7 +5856,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>122</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -5862,12 +5866,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>258.9</t>
+          <t>264.6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -5910,7 +5914,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>122</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -5920,12 +5924,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>259.1</t>
+          <t>264.5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.07</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -5978,12 +5982,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>115.1</t>
+          <t>103.6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>147.66</t>
+          <t>87.84</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -6035,17 +6039,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>461</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>223.5</t>
+          <t>222.6</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1800.06</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -6098,12 +6102,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -6160,12 +6164,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>256.8</t>
+          <t>262.1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1800.07</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -6208,22 +6212,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>645</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>645</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -6270,22 +6274,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>565</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>565</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>195.8</t>
+          <t>254.2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>295.87</t>
+          <t>879.45</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -6342,12 +6346,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>167.4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>279.17</t>
+          <t>306.77</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -6394,22 +6398,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>821</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>821</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -6456,7 +6460,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>425</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -6466,7 +6470,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>276.7</t>
+          <t>295.3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -6524,7 +6528,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>334.6</t>
+          <t>347.5</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -6648,22 +6652,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -6720,12 +6724,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>86.21</t>
+          <t>57.65</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -6782,12 +6786,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -6844,12 +6848,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>14.50</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -6906,7 +6910,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -6973,7 +6977,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -7030,12 +7034,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -7082,7 +7086,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -7092,7 +7096,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>280.2</t>
+          <t>292.7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -7150,12 +7154,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -7212,12 +7216,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -7279,7 +7283,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>79.67</t>
+          <t>70.16</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -7336,12 +7340,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -7398,12 +7402,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>280.8</t>
+          <t>287.2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1800.06</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -7456,12 +7460,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>279.8</t>
+          <t>287.1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1800.09</t>
+          <t>1800.01</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -7514,12 +7518,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.4</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>243.09</t>
+          <t>207.43</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -7566,22 +7570,22 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>267</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>650</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>258.8</t>
+          <t>258.2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1800.07</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -7634,12 +7638,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -7696,7 +7700,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>276.9</t>
+          <t>277.3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -7744,22 +7748,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>775</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>775</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -7806,22 +7810,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>677</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>677</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>241.6</t>
+          <t>281.1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>665.90</t>
+          <t>998.50</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -7878,12 +7882,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>174.7</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>385.08</t>
+          <t>439.38</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -7930,22 +7934,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>985</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>985</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -8002,12 +8006,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>329.5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1800.03</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -8060,12 +8064,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>337.1</t>
+          <t>365.2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1800.06</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
